--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.8472931062797</v>
+        <v>2.412685129770451</v>
       </c>
       <c r="D2" t="n">
-        <v>15.36775507349987</v>
+        <v>2.497260199443728</v>
       </c>
       <c r="E2" t="n">
-        <v>10.28071683696142</v>
+        <v>1.67061648600623</v>
       </c>
       <c r="F2" t="n">
-        <v>10.55020364818948</v>
+        <v>1.714408092830791</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.02274667178924</v>
+        <v>5.528696334165752</v>
       </c>
       <c r="D3" t="n">
-        <v>36.24928537942656</v>
+        <v>5.890508874156816</v>
       </c>
       <c r="E3" t="n">
-        <v>10.28071683696142</v>
+        <v>1.67061648600623</v>
       </c>
       <c r="F3" t="n">
-        <v>10.55020364818948</v>
+        <v>1.714408092830791</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.612858062742252</v>
+        <v>1.562089435195616</v>
       </c>
       <c r="D4" t="n">
-        <v>10.10015059937961</v>
+        <v>1.641274472399187</v>
       </c>
       <c r="E4" t="n">
-        <v>10.28071683696142</v>
+        <v>1.67061648600623</v>
       </c>
       <c r="F4" t="n">
-        <v>10.55020364818948</v>
+        <v>1.714408092830791</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.26139597769051</v>
+        <v>2.154976846374707</v>
       </c>
       <c r="D5" t="n">
-        <v>12.61181379002013</v>
+        <v>2.049419740878272</v>
       </c>
       <c r="E5" t="n">
-        <v>10.28071683696142</v>
+        <v>1.67061648600623</v>
       </c>
       <c r="F5" t="n">
-        <v>10.55020364818948</v>
+        <v>1.714408092830791</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.69318613769528</v>
+        <v>3.200142747375483</v>
       </c>
       <c r="D6" t="n">
-        <v>19.14796409472214</v>
+        <v>3.111544165392348</v>
       </c>
       <c r="E6" t="n">
-        <v>10.28071683696142</v>
+        <v>1.67061648600623</v>
       </c>
       <c r="F6" t="n">
-        <v>10.55020364818948</v>
+        <v>1.714408092830791</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.27726725656808</v>
+        <v>6.220055929192314</v>
       </c>
       <c r="D7" t="n">
-        <v>38.11130323432501</v>
+        <v>6.193086775577815</v>
       </c>
       <c r="E7" t="n">
-        <v>10.28071683696142</v>
+        <v>1.67061648600623</v>
       </c>
       <c r="F7" t="n">
-        <v>10.55020364818948</v>
+        <v>1.714408092830791</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.85993321668391</v>
+        <v>4.689739147711136</v>
       </c>
       <c r="D8" t="n">
-        <v>28.29351386337386</v>
+        <v>4.597696002798253</v>
       </c>
       <c r="E8" t="n">
-        <v>10.28071683696142</v>
+        <v>1.67061648600623</v>
       </c>
       <c r="F8" t="n">
-        <v>10.55020364818948</v>
+        <v>1.714408092830791</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
